--- a/submissions/02-title-exam-cedarbrook-lot12/inputs/court_records_search_hlt262214.xlsx
+++ b/submissions/02-title-exam-cedarbrook-lot12/inputs/court_records_search_hlt262214.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C63EA8-873B-5340-AD1F-B15778D85711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77743B2F-6BD6-D74F-87FA-8FE87039B6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
